--- a/Esami_date.xlsx
+++ b/Esami_date.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabri\Desktop\Informatica_Uni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AC3E846-92D5-43D1-B50A-43173FC11C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA11A1D9-B36C-4F3C-9E51-E040F26DB26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99BD12D4-B8E6-49E2-9F85-BAFC211A9808}"/>
   </bookViews>
@@ -660,7 +660,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="9">
         <v>18</v>
@@ -735,7 +735,9 @@
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6">
+        <v>28</v>
+      </c>
       <c r="C7" s="6">
         <v>24</v>
       </c>
